--- a/RoboticEnterpriseFramework/Data/Config.xlsx
+++ b/RoboticEnterpriseFramework/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\UiPath\RoboticEnterpriseFramework\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\Sem 7 RPA\RoboticEnterpriseFramework\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCFFAF6-B828-4174-8AD3-C69AA05120E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9743247E-FA0D-4406-8915-6D221C6DDFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -159,22 +159,22 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
+    <t>FilePath</t>
+  </si>
+  <si>
+    <t>Data\Input\Book1.xlsx</t>
+  </si>
+  <si>
+    <t>FileSheetName</t>
+  </si>
+  <si>
+    <t>Sheet1</t>
+  </si>
+  <si>
+    <t>TNEA2024</t>
+  </si>
+  <si>
     <t>ARPA</t>
-  </si>
-  <si>
-    <t>FilePath</t>
-  </si>
-  <si>
-    <t>Data\Input\Book1.xlsx</t>
-  </si>
-  <si>
-    <t>Sheet1</t>
-  </si>
-  <si>
-    <t>FileSheetName</t>
-  </si>
-  <si>
-    <t>TNEA-2024</t>
   </si>
 </sst>
 </file>
@@ -551,12 +551,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43.5546875" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="81.44140625" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -598,25 +598,25 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.2">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="28.8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -630,16 +630,16 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
         <v>47</v>
@@ -1644,12 +1644,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="75.44140625" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1686,7 +1686,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="28.8">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="45">
+    <row r="17" spans="1:3" ht="28.8">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2802,12 +2802,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" customWidth="1"/>
+    <col min="3" max="3" width="60.33203125" customWidth="1"/>
+    <col min="4" max="26" width="65.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
